--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.24626150921413</v>
+        <v>3.452517495247296</v>
       </c>
       <c r="D2" t="n">
-        <v>41.15802138016474</v>
+        <v>6.68817847427677</v>
       </c>
       <c r="E2" t="n">
-        <v>24.61513363496578</v>
+        <v>3.99995921568194</v>
       </c>
       <c r="F2" t="n">
-        <v>21.68699782081302</v>
+        <v>3.524137145882115</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.1249593292881</v>
+        <v>3.757805891009316</v>
       </c>
       <c r="D3" t="n">
-        <v>23.43108721460467</v>
+        <v>3.807551672373259</v>
       </c>
       <c r="E3" t="n">
-        <v>24.61513363496578</v>
+        <v>3.99995921568194</v>
       </c>
       <c r="F3" t="n">
-        <v>21.68699782081302</v>
+        <v>3.524137145882115</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>82.45712484462287</v>
+        <v>13.39928278725122</v>
       </c>
       <c r="D4" t="n">
-        <v>82.68964607046568</v>
+        <v>13.43706748645067</v>
       </c>
       <c r="E4" t="n">
-        <v>24.61513363496578</v>
+        <v>3.99995921568194</v>
       </c>
       <c r="F4" t="n">
-        <v>21.68699782081302</v>
+        <v>3.524137145882115</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.61110172983739</v>
+        <v>6.924304031098576</v>
       </c>
       <c r="D5" t="n">
-        <v>42.6564370657882</v>
+        <v>6.931671023190582</v>
       </c>
       <c r="E5" t="n">
-        <v>24.61513363496578</v>
+        <v>3.99995921568194</v>
       </c>
       <c r="F5" t="n">
-        <v>21.68699782081302</v>
+        <v>3.524137145882115</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
